--- a/site/exports/tongji-math.xlsx
+++ b/site/exports/tongji-math.xlsx
@@ -1058,7 +1058,7 @@
       <c r="J6" s="2" t="inlineStr"/>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr"/>
@@ -1123,7 +1123,7 @@
       <c r="J7" s="2" t="inlineStr"/>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr"/>
